--- a/pipeline/meta_data.xlsx
+++ b/pipeline/meta_data.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mht541\Documents\Python_Scripts\2DLC_workflow\matlab\utils\NTS_featuredetection\pipeline\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mht541\Desktop\test_mosaic\pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5105D3-4159-4FB1-9773-1CB7FF11BB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12165838-0DB3-42E4-8BF7-8CE007EA9900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-9705" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{DFCCBFE7-D459-41E5-B69A-B893D40D8EA8}"/>
+    <workbookView xWindow="-975" yWindow="-11910" windowWidth="21600" windowHeight="11295" xr2:uid="{DFCCBFE7-D459-41E5-B69A-B893D40D8EA8}"/>
   </bookViews>
   <sheets>
     <sheet name="input_parameters" sheetId="1" r:id="rId1"/>
     <sheet name="IS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
   <si>
     <t>Paths</t>
   </si>
@@ -204,9 +205,6 @@
     <t>ROI</t>
   </si>
   <si>
-    <t>C:\Users\mht541\Documents\2D_LC_IMS_R\2DIMS\regionofinterest</t>
-  </si>
-  <si>
     <t>CDF_dir</t>
   </si>
   <si>
@@ -249,12 +247,6 @@
     <t>ROI_optimization_stepsize_of_mzerror_</t>
   </si>
   <si>
-    <t>sparse_tensor_toolbox</t>
-  </si>
-  <si>
-    <t>C:\Users\mht541\Documents\Python_Scripts\2DLC_workflow\matlab\tensor_toolbox</t>
-  </si>
-  <si>
     <t>phase_shift</t>
   </si>
   <si>
@@ -267,12 +259,6 @@
     <t>Inchikey</t>
   </si>
   <si>
-    <t>F:\Nadine\cdf</t>
-  </si>
-  <si>
-    <t>F:\Nadine\Mosaic_100</t>
-  </si>
-  <si>
     <t xml:space="preserve">NumTrace </t>
   </si>
   <si>
@@ -283,6 +269,12 @@
   </si>
   <si>
     <t>number of MS traces</t>
+  </si>
+  <si>
+    <t>D:\Vandalf\CDF\Phase3_Positive\SCAN</t>
+  </si>
+  <si>
+    <t>C:\Users\mht541\Desktop\public_mosaic</t>
   </si>
 </sst>
 </file>
@@ -775,10 +767,10 @@
         <v>54</v>
       </c>
       <c r="P1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q1" t="s">
         <v>67</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -816,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="O2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P2">
         <v>4</v>
@@ -834,7 +826,7 @@
         <v>10</v>
       </c>
       <c r="E3">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -858,13 +850,13 @@
         <v>50</v>
       </c>
       <c r="O3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -872,7 +864,7 @@
         <v>52</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -908,16 +900,11 @@
         <v>1</v>
       </c>
       <c r="Q4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="B5" s="4"/>
       <c r="D5" t="s">
         <v>16</v>
       </c>
@@ -931,10 +918,10 @@
         <v>19</v>
       </c>
       <c r="O5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="Q5" t="s">
         <v>12</v>
@@ -942,10 +929,10 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -957,7 +944,7 @@
         <v>15</v>
       </c>
       <c r="O6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -967,12 +954,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>71</v>
-      </c>
+      <c r="B7" s="4"/>
       <c r="D7" t="s">
         <v>26</v>
       </c>
@@ -983,13 +965,13 @@
         <v>27</v>
       </c>
       <c r="O7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P7">
         <v>4</v>
       </c>
       <c r="Q7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -1000,10 +982,10 @@
         <v>0.7</v>
       </c>
       <c r="O8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P8">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1016,14 +998,14 @@
       <c r="F9" t="s">
         <v>33</v>
       </c>
-      <c r="O9" s="5" t="s">
-        <v>62</v>
+      <c r="O9" t="s">
+        <v>61</v>
       </c>
       <c r="P9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -1037,13 +1019,13 @@
         <v>33</v>
       </c>
       <c r="O10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P10">
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -1147,35 +1129,35 @@
     </row>
     <row r="20" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E20">
-        <v>1.48</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1205,7 +1187,7 @@
         <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
